--- a/data/nzd0013/nzd0013.xlsx
+++ b/data/nzd0013/nzd0013.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D219"/>
+  <dimension ref="A1:D220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4370,6 +4370,24 @@
         <v>381.45</v>
       </c>
       <c r="D219" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>366.72</v>
+      </c>
+      <c r="C220" t="n">
+        <v>382.05</v>
+      </c>
+      <c r="D220" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -4386,7 +4404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B284"/>
+  <dimension ref="A1:B285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7229,6 +7247,16 @@
       </c>
       <c r="B284" t="n">
         <v>-0.24</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>-0.91</v>
       </c>
     </row>
   </sheetData>
@@ -7397,28 +7425,28 @@
         <v>0.0434</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.018780971014785</v>
+        <v>-1.031069424307726</v>
       </c>
       <c r="J2" t="n">
+        <v>219</v>
+      </c>
+      <c r="K2" t="n">
         <v>218</v>
       </c>
-      <c r="K2" t="n">
-        <v>217</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.1340956762536684</v>
+        <v>0.1376964235344533</v>
       </c>
       <c r="M2" t="n">
-        <v>17.42108087677977</v>
+        <v>17.39915807965982</v>
       </c>
       <c r="N2" t="n">
-        <v>432.7613802846287</v>
+        <v>431.8412840699324</v>
       </c>
       <c r="O2" t="n">
-        <v>20.80291759068013</v>
+        <v>20.78079122819755</v>
       </c>
       <c r="P2" t="n">
-        <v>409.4663958494185</v>
+        <v>409.5873596500643</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -7475,28 +7503,28 @@
         <v>0.0697</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1192031420387581</v>
+        <v>0.1171615721777026</v>
       </c>
       <c r="J3" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K3" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04484798414828128</v>
+        <v>0.04370746339134923</v>
       </c>
       <c r="M3" t="n">
-        <v>3.500695474646783</v>
+        <v>3.496945655092285</v>
       </c>
       <c r="N3" t="n">
-        <v>19.78369613543935</v>
+        <v>19.72325515195724</v>
       </c>
       <c r="O3" t="n">
-        <v>4.447886704429346</v>
+        <v>4.441087158788627</v>
       </c>
       <c r="P3" t="n">
-        <v>381.4163951084471</v>
+        <v>381.4362751344435</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -7534,7 +7562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D219"/>
+  <dimension ref="A1:D220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12351,6 +12379,28 @@
         </is>
       </c>
     </row>
+    <row r="220">
+      <c r="A220" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>-34.72295638137953,173.09161930271753</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>-34.723624683741434,173.09203579647905</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0013/nzd0013.xlsx
+++ b/data/nzd0013/nzd0013.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D220"/>
+  <dimension ref="A1:D223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4388,6 +4388,60 @@
         <v>382.05</v>
       </c>
       <c r="D220" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>369.95</v>
+      </c>
+      <c r="C221" t="n">
+        <v>382.32</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>377.63</v>
+      </c>
+      <c r="C222" t="n">
+        <v>383.49</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-27 22:17:28+00:00</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>377.63</v>
+      </c>
+      <c r="C223" t="n">
+        <v>381.82</v>
+      </c>
+      <c r="D223" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -4404,7 +4458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B285"/>
+  <dimension ref="A1:B288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7257,6 +7311,36 @@
       </c>
       <c r="B285" t="n">
         <v>-0.91</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-08-27 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>
@@ -7425,28 +7509,28 @@
         <v>0.0434</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.031069424307726</v>
+        <v>-1.046603445740397</v>
       </c>
       <c r="J2" t="n">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="K2" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1376964235344533</v>
+        <v>0.1443682367155875</v>
       </c>
       <c r="M2" t="n">
-        <v>17.39915807965982</v>
+        <v>17.2364188087486</v>
       </c>
       <c r="N2" t="n">
-        <v>431.8412840699324</v>
+        <v>426.7416075368657</v>
       </c>
       <c r="O2" t="n">
-        <v>20.78079122819755</v>
+        <v>20.65772512976358</v>
       </c>
       <c r="P2" t="n">
-        <v>409.5873596500643</v>
+        <v>409.7409540939075</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -7503,28 +7587,28 @@
         <v>0.0697</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1171615721777026</v>
+        <v>0.1124206501119458</v>
       </c>
       <c r="J3" t="n">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="K3" t="n">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04370746339134923</v>
+        <v>0.04130966246812662</v>
       </c>
       <c r="M3" t="n">
-        <v>3.496945655092285</v>
+        <v>3.477842556928856</v>
       </c>
       <c r="N3" t="n">
-        <v>19.72325515195724</v>
+        <v>19.51830405251814</v>
       </c>
       <c r="O3" t="n">
-        <v>4.441087158788627</v>
+        <v>4.417952472867735</v>
       </c>
       <c r="P3" t="n">
-        <v>381.4362751344435</v>
+        <v>381.4826857382482</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -7562,7 +7646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D220"/>
+  <dimension ref="A1:D223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12401,6 +12485,72 @@
         </is>
       </c>
     </row>
+    <row r="221">
+      <c r="A221" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>-34.72294807667653,173.09165311654488</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>-34.72362398953309,173.09203862304213</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>-34.72292833047196,173.0917335159586</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>-34.72362098129616,173.09205087148163</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-27 22:17:28+00:00</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>-34.72292833047196,173.0917335159586</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>-34.72362527510405,173.092033388666</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0013/nzd0013.xlsx
+++ b/data/nzd0013/nzd0013.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D223"/>
+  <dimension ref="A1:D224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4436,12 +4436,30 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>377.63</v>
+        <v>376.71</v>
       </c>
       <c r="C223" t="n">
         <v>381.82</v>
       </c>
       <c r="D223" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>374.89</v>
+      </c>
+      <c r="C224" t="n">
+        <v>383.64</v>
+      </c>
+      <c r="D224" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -4458,7 +4476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B288"/>
+  <dimension ref="A1:B289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7341,6 +7359,16 @@
       </c>
       <c r="B288" t="n">
         <v>0.03</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -7509,28 +7537,28 @@
         <v>0.0434</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.046603445740397</v>
+        <v>-1.052310994435015</v>
       </c>
       <c r="J2" t="n">
+        <v>223</v>
+      </c>
+      <c r="K2" t="n">
         <v>222</v>
       </c>
-      <c r="K2" t="n">
-        <v>221</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.1443682367155875</v>
+        <v>0.146757212687489</v>
       </c>
       <c r="M2" t="n">
-        <v>17.2364188087486</v>
+        <v>17.18573229548361</v>
       </c>
       <c r="N2" t="n">
-        <v>426.7416075368657</v>
+        <v>425.0399250892011</v>
       </c>
       <c r="O2" t="n">
-        <v>20.65772512976358</v>
+        <v>20.61649643099431</v>
       </c>
       <c r="P2" t="n">
-        <v>409.7409540939075</v>
+        <v>409.7977392946124</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -7587,28 +7615,28 @@
         <v>0.0697</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1124206501119458</v>
+        <v>0.1117385510879417</v>
       </c>
       <c r="J3" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K3" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04130966246812662</v>
+        <v>0.0411696625385779</v>
       </c>
       <c r="M3" t="n">
-        <v>3.477842556928856</v>
+        <v>3.466348442603363</v>
       </c>
       <c r="N3" t="n">
-        <v>19.51830405251814</v>
+        <v>19.43429134809854</v>
       </c>
       <c r="O3" t="n">
-        <v>4.417952472867735</v>
+        <v>4.408434115204461</v>
       </c>
       <c r="P3" t="n">
-        <v>381.4826857382482</v>
+        <v>381.4894034800785</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -7646,7 +7674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D223"/>
+  <dimension ref="A1:D224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12537,7 +12565,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>-34.72292833047196,173.0917335159586</t>
+          <t>-34.722930695905525,173.09172388478086</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -12546,6 +12574,28 @@
         </is>
       </c>
       <c r="D223" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>-34.722935375347916,173.0917048317972</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>-34.723620595624666,173.09205244179432</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
